--- a/gte/nodes/LPC/compressor_blade_parameters.xlsx
+++ b/gte/nodes/LPC/compressor_blade_parameters.xlsx
@@ -806,121 +806,121 @@
         <v>122</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>43.690571470396783</v>
+        <v>43.547726728055785</v>
       </c>
       <c r="E3">
-        <v>42.454746312676981</v>
+        <v>42.456728068641723</v>
       </c>
       <c r="F3">
-        <v>81.09635179412308</v>
+        <v>81.006607150104657</v>
       </c>
       <c r="G3">
-        <v>80.776956372261765</v>
+        <v>80.768336799680483</v>
       </c>
       <c r="H3">
-        <v>104.53435477471319</v>
+        <v>91.467560427874034</v>
       </c>
       <c r="I3">
         <v>143.00704677873924</v>
       </c>
       <c r="J3">
-        <v>224.36663340756778</v>
+        <v>196.32080423162179</v>
       </c>
       <c r="K3">
-        <v>200.73241437590545</v>
+        <v>149.67036192155513</v>
       </c>
       <c r="L3">
-        <v>1995.5069727926405</v>
+        <v>1746.0686011935602</v>
       </c>
       <c r="M3">
         <v>5214.1702647945895</v>
       </c>
       <c r="N3">
-        <v>19.08948476405914</v>
+        <v>19.089484764059137</v>
       </c>
       <c r="O3">
         <v>36.460932396303264</v>
       </c>
       <c r="P3">
-        <v>2.1463435048803872</v>
+        <v>2.1463435048803867</v>
       </c>
       <c r="Q3">
-        <v>1.4036540079488462</v>
+        <v>1.0465943133076889</v>
       </c>
       <c r="R3">
-        <v>601.59522627742638</v>
+        <v>511.49201365934181</v>
       </c>
       <c r="S3">
-        <v>360.84641998699266</v>
+        <v>223.27382497456841</v>
       </c>
       <c r="T3">
-        <v>48736.943038917969</v>
+        <v>42644.825159053216</v>
       </c>
       <c r="U3">
         <v>243224.91593453163</v>
       </c>
       <c r="V3">
-        <v>4452.7769850555978</v>
+        <v>3896.1798619236479</v>
       </c>
       <c r="W3">
-        <v>7610.7258758965027</v>
+        <v>5674.7984276026973</v>
       </c>
       <c r="X3">
-        <v>120.02735995121444</v>
+        <v>90.1201306239064</v>
       </c>
       <c r="Y3">
-        <v>79.087562023004324</v>
+        <v>66.629675316765116</v>
       </c>
       <c r="Z3">
-        <v>10643.743085219083</v>
+        <v>9313.2751995666968</v>
       </c>
       <c r="AA3">
         <v>53111.406407041417</v>
       </c>
       <c r="AB3">
-        <v>169.73355505859129</v>
+        <v>148.51686067626869</v>
       </c>
       <c r="AC3">
-        <v>291.83488558988063</v>
+        <v>217.67747985063272</v>
       </c>
       <c r="AD3">
-        <v>0.923784490912283</v>
+        <v>0.92229276830267226</v>
       </c>
       <c r="AE3">
-        <v>0.31528382193045834</v>
+        <v>0.23511685094091103</v>
       </c>
       <c r="AF3">
-        <v>117.29049494700097</v>
+        <v>87.729241455364473</v>
       </c>
       <c r="AG3">
-        <v>77.481654090600728</v>
+        <v>65.736417012307314</v>
       </c>
       <c r="AH3">
-        <v>10646.479950223296</v>
+        <v>9315.6660887352373</v>
       </c>
       <c r="AI3">
-        <v>53113.012314973814</v>
+        <v>53112.299665345869</v>
       </c>
       <c r="AJ3">
-        <v>-4.325851538926287E-14</v>
+        <v>2.1629257694631435E-14</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>-3.5982048360327496E-14</v>
       </c>
       <c r="AL3">
-        <v>10763.770445170296</v>
+        <v>9403.395330190604</v>
       </c>
       <c r="AM3">
-        <v>53190.493969064417</v>
+        <v>53178.036082358187</v>
       </c>
       <c r="AN3">
-        <v>462.40518694834083</v>
+        <v>403.96427978050838</v>
       </c>
       <c r="AO3">
-        <v>1200.866149310031</v>
+        <v>1200.8526725638205</v>
       </c>
       <c r="AP3">
         <v>14.793838572448902</v>
@@ -946,31 +946,31 @@
         <v>59</v>
       </c>
       <c r="D4">
-        <v>56.072501839486684</v>
+        <v>55.871402933226911</v>
       </c>
       <c r="E4">
-        <v>54.121387867884273</v>
+        <v>54.149577308386313</v>
       </c>
       <c r="F4">
-        <v>86.576447604888187</v>
+        <v>86.599495819297161</v>
       </c>
       <c r="G4">
-        <v>86.295359119488154</v>
+        <v>86.2973258273861</v>
       </c>
       <c r="H4">
-        <v>168.94859367331856</v>
+        <v>147.83001946415376</v>
       </c>
       <c r="I4">
         <v>163.2443505702883</v>
       </c>
       <c r="J4">
-        <v>577.82181938928818</v>
+        <v>505.56145675216379</v>
       </c>
       <c r="K4">
-        <v>201.57183521836788</v>
+        <v>216.71495084244356</v>
       </c>
       <c r="L4">
-        <v>4100.1198982596379</v>
+        <v>3587.6049109771834</v>
       </c>
       <c r="M4">
         <v>6359.2557610133372</v>
@@ -982,82 +982,82 @@
         <v>38.955441574532315</v>
       </c>
       <c r="P4">
-        <v>3.420104345506259</v>
+        <v>3.4198835837585326</v>
       </c>
       <c r="Q4">
-        <v>1.2347859788971802</v>
+        <v>1.3275494685442875</v>
       </c>
       <c r="R4">
-        <v>2358.4013959487852</v>
+        <v>2024.6708666215684</v>
       </c>
       <c r="S4">
-        <v>340.18163097104696</v>
+        <v>382.84758624176931</v>
       </c>
       <c r="T4">
-        <v>127306.1432527935</v>
+        <v>111392.87534619434</v>
       </c>
       <c r="U4">
         <v>316934.49238931114</v>
       </c>
       <c r="V4">
-        <v>14575.403455900161</v>
+        <v>12753.478023912641</v>
       </c>
       <c r="W4">
-        <v>8165.507408989437</v>
+        <v>8778.9132758991727</v>
       </c>
       <c r="X4">
-        <v>382.19048052714834</v>
+        <v>295.70954009379392</v>
       </c>
       <c r="Y4">
-        <v>91.283555102833432</v>
+        <v>95.147768425281939</v>
       </c>
       <c r="Z4">
-        <v>27802.603065826464</v>
+        <v>24327.277682598167</v>
       </c>
       <c r="AA4">
         <v>69206.876133648</v>
       </c>
       <c r="AB4">
-        <v>552.5655747656931</v>
+        <v>484.28688385028033</v>
       </c>
       <c r="AC4">
-        <v>313.18755906905062</v>
+        <v>336.686670028717</v>
       </c>
       <c r="AD4">
-        <v>1.1539778912488536</v>
+        <v>1.1540064426669374</v>
       </c>
       <c r="AE4">
-        <v>0.25962063569928129</v>
+        <v>0.27911492408533461</v>
       </c>
       <c r="AF4">
-        <v>371.0599104135274</v>
+        <v>285.95409609648021</v>
       </c>
       <c r="AG4">
-        <v>89.864418992600932</v>
+        <v>93.507594951295388</v>
       </c>
       <c r="AH4">
-        <v>27813.733635940083</v>
+        <v>24337.033126595481</v>
       </c>
       <c r="AI4">
-        <v>69208.295269758208</v>
+        <v>69208.516307121958</v>
       </c>
       <c r="AJ4">
-        <v>-1.1299590031018362E-13</v>
+        <v>0</v>
       </c>
       <c r="AK4">
         <v>0</v>
       </c>
       <c r="AL4">
-        <v>28184.793546353609</v>
+        <v>24622.987222691965</v>
       </c>
       <c r="AM4">
-        <v>69298.15968875082</v>
+        <v>69302.023902073284</v>
       </c>
       <c r="AN4">
-        <v>950.10957599272524</v>
+        <v>830.04177351674593</v>
       </c>
       <c r="AO4">
-        <v>1464.576851344719</v>
+        <v>1464.5807754706079</v>
       </c>
       <c r="AP4">
         <v>18.807394940918407</v>
@@ -1083,100 +1083,100 @@
         <v>49</v>
       </c>
       <c r="D5">
-        <v>65.723482777139381</v>
+        <v>65.54754254542631</v>
       </c>
       <c r="E5">
-        <v>64.719130417759587</v>
+        <v>64.790281795512556</v>
       </c>
       <c r="F5">
-        <v>80.311624104604832</v>
+        <v>79.861855803663119</v>
       </c>
       <c r="G5">
-        <v>75.884849915981761</v>
+        <v>75.72046164456286</v>
       </c>
       <c r="H5">
-        <v>120.92057816393815</v>
+        <v>90.69043362295362</v>
       </c>
       <c r="I5">
         <v>410.0602845013932</v>
       </c>
       <c r="J5">
-        <v>409.55703983306262</v>
+        <v>307.16777987479696</v>
       </c>
       <c r="K5">
-        <v>2642.0962031208687</v>
+        <v>2457.9997342357115</v>
       </c>
       <c r="L5">
-        <v>3510.9933395076941</v>
+        <v>2633.2450046307713</v>
       </c>
       <c r="M5">
-        <v>13866.959326974131</v>
+        <v>13866.959326974129</v>
       </c>
       <c r="N5">
-        <v>29.0355321883068</v>
+        <v>29.035532188306803</v>
       </c>
       <c r="O5">
-        <v>33.816879739610627</v>
+        <v>33.81687973961062</v>
       </c>
       <c r="P5">
-        <v>3.386992074068695</v>
+        <v>3.3869920740686945</v>
       </c>
       <c r="Q5">
-        <v>6.4431897040053192</v>
+        <v>5.9942399377313027</v>
       </c>
       <c r="R5">
-        <v>1572.0319162804947</v>
+        <v>1163.0699361322081</v>
       </c>
       <c r="S5">
-        <v>20045.971858200406</v>
+        <v>17546.038258258461</v>
       </c>
       <c r="T5">
-        <v>130423.20823184408</v>
+        <v>97817.406173883079</v>
       </c>
       <c r="U5">
         <v>599964.56867843145</v>
       </c>
       <c r="V5">
-        <v>12362.714396622943</v>
+        <v>9272.0357974672115</v>
       </c>
       <c r="W5">
-        <v>92836.431152040343</v>
+        <v>86376.48795118423</v>
       </c>
       <c r="X5">
-        <v>184.86546848687544</v>
+        <v>122.69510028699325</v>
       </c>
       <c r="Y5">
-        <v>3022.4448052604748</v>
+        <v>2812.1980843698334</v>
       </c>
       <c r="Z5">
-        <v>28479.648109637637</v>
+        <v>21359.736082228235</v>
       </c>
       <c r="AA5">
-        <v>131027.27276407532</v>
+        <v>131027.27276407558</v>
       </c>
       <c r="AB5">
-        <v>471.00778360240759</v>
+        <v>353.25583770180572</v>
       </c>
       <c r="AC5">
-        <v>3488.9815906200974</v>
+        <v>3254.6065385403167</v>
       </c>
       <c r="AD5">
-        <v>0.95341937133245336</v>
+        <v>0.95270365782363642</v>
       </c>
       <c r="AE5">
-        <v>1.5601462650526363</v>
+        <v>1.4531462890140428</v>
       </c>
       <c r="AF5">
-        <v>177.02703078190297</v>
+        <v>116.82068594496569</v>
       </c>
       <c r="AG5">
-        <v>2927.417433775172</v>
+        <v>2729.636440802064</v>
       </c>
       <c r="AH5">
-        <v>28487.486547342607</v>
+        <v>21365.610496570262</v>
       </c>
       <c r="AI5">
-        <v>131122.30013556063</v>
+        <v>131109.83440764336</v>
       </c>
       <c r="AJ5">
         <v>0</v>
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>28664.513578124512</v>
+        <v>21482.431182515225</v>
       </c>
       <c r="AM5">
-        <v>134049.71756933577</v>
+        <v>133839.47084844543</v>
       </c>
       <c r="AN5">
-        <v>809.33128774935858</v>
+        <v>606.54801085480688</v>
       </c>
       <c r="AO5">
-        <v>3225.2008587498917</v>
+        <v>3225.3592428517177</v>
       </c>
       <c r="AP5">
         <v>22.501758500453995</v>
@@ -1681,121 +1681,121 @@
         <v>122</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>43.690571470396783</v>
+        <v>43.547726728055785</v>
       </c>
       <c r="E3">
-        <v>42.454746312676981</v>
+        <v>42.456728068641723</v>
       </c>
       <c r="F3">
-        <v>81.09635179412308</v>
+        <v>81.006607150104657</v>
       </c>
       <c r="G3">
-        <v>80.776956372261765</v>
+        <v>80.768336799680483</v>
       </c>
       <c r="H3">
-        <v>104.53435477471319</v>
+        <v>91.467560427874034</v>
       </c>
       <c r="I3">
         <v>143.00704677873924</v>
       </c>
       <c r="J3">
-        <v>224.36663340756778</v>
+        <v>196.32080423162179</v>
       </c>
       <c r="K3">
-        <v>200.73241437590545</v>
+        <v>149.67036192155513</v>
       </c>
       <c r="L3">
-        <v>1995.5069727926405</v>
+        <v>1746.0686011935602</v>
       </c>
       <c r="M3">
         <v>5214.1702647945895</v>
       </c>
       <c r="N3">
-        <v>19.08948476405914</v>
+        <v>19.089484764059137</v>
       </c>
       <c r="O3">
         <v>36.460932396303264</v>
       </c>
       <c r="P3">
-        <v>2.1463435048803872</v>
+        <v>2.1463435048803867</v>
       </c>
       <c r="Q3">
-        <v>1.4036540079488462</v>
+        <v>1.0465943133076889</v>
       </c>
       <c r="R3">
-        <v>601.59522627742638</v>
+        <v>511.49201365934181</v>
       </c>
       <c r="S3">
-        <v>360.84641998699266</v>
+        <v>223.27382497456841</v>
       </c>
       <c r="T3">
-        <v>48736.943038917969</v>
+        <v>42644.825159053216</v>
       </c>
       <c r="U3">
         <v>243224.91593453163</v>
       </c>
       <c r="V3">
-        <v>4452.7769850555978</v>
+        <v>3896.1798619236479</v>
       </c>
       <c r="W3">
-        <v>7610.7258758965027</v>
+        <v>5674.7984276026973</v>
       </c>
       <c r="X3">
-        <v>120.02735995121444</v>
+        <v>90.1201306239064</v>
       </c>
       <c r="Y3">
-        <v>79.087562023004324</v>
+        <v>66.629675316765116</v>
       </c>
       <c r="Z3">
-        <v>10643.743085219083</v>
+        <v>9313.2751995666968</v>
       </c>
       <c r="AA3">
         <v>53111.406407041417</v>
       </c>
       <c r="AB3">
-        <v>169.73355505859129</v>
+        <v>148.51686067626869</v>
       </c>
       <c r="AC3">
-        <v>291.83488558988063</v>
+        <v>217.67747985063272</v>
       </c>
       <c r="AD3">
-        <v>0.923784490912283</v>
+        <v>0.92229276830267226</v>
       </c>
       <c r="AE3">
-        <v>0.31528382193045834</v>
+        <v>0.23511685094091103</v>
       </c>
       <c r="AF3">
-        <v>117.29049494700097</v>
+        <v>87.729241455364473</v>
       </c>
       <c r="AG3">
-        <v>77.481654090600728</v>
+        <v>65.736417012307314</v>
       </c>
       <c r="AH3">
-        <v>10646.479950223296</v>
+        <v>9315.6660887352373</v>
       </c>
       <c r="AI3">
-        <v>53113.012314973814</v>
+        <v>53112.299665345869</v>
       </c>
       <c r="AJ3">
-        <v>-4.325851538926287E-14</v>
+        <v>2.1629257694631435E-14</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>-3.5982048360327496E-14</v>
       </c>
       <c r="AL3">
-        <v>10763.770445170296</v>
+        <v>9403.395330190604</v>
       </c>
       <c r="AM3">
-        <v>53190.493969064417</v>
+        <v>53178.036082358187</v>
       </c>
       <c r="AN3">
-        <v>462.40518694834083</v>
+        <v>403.96427978050838</v>
       </c>
       <c r="AO3">
-        <v>1200.866149310031</v>
+        <v>1200.8526725638205</v>
       </c>
       <c r="AP3">
         <v>14.793838572448902</v>
@@ -1821,31 +1821,31 @@
         <v>59</v>
       </c>
       <c r="D4">
-        <v>56.072501839486684</v>
+        <v>55.871402933226911</v>
       </c>
       <c r="E4">
-        <v>54.121387867884273</v>
+        <v>54.149577308386313</v>
       </c>
       <c r="F4">
-        <v>86.576447604888187</v>
+        <v>86.599495819297161</v>
       </c>
       <c r="G4">
-        <v>86.295359119488154</v>
+        <v>86.2973258273861</v>
       </c>
       <c r="H4">
-        <v>168.94859367331856</v>
+        <v>147.83001946415376</v>
       </c>
       <c r="I4">
         <v>163.2443505702883</v>
       </c>
       <c r="J4">
-        <v>577.82181938928818</v>
+        <v>505.56145675216379</v>
       </c>
       <c r="K4">
-        <v>201.57183521836788</v>
+        <v>216.71495084244356</v>
       </c>
       <c r="L4">
-        <v>4100.1198982596379</v>
+        <v>3587.6049109771834</v>
       </c>
       <c r="M4">
         <v>6359.2557610133372</v>
@@ -1857,82 +1857,82 @@
         <v>38.955441574532315</v>
       </c>
       <c r="P4">
-        <v>3.420104345506259</v>
+        <v>3.4198835837585326</v>
       </c>
       <c r="Q4">
-        <v>1.2347859788971802</v>
+        <v>1.3275494685442875</v>
       </c>
       <c r="R4">
-        <v>2358.4013959487852</v>
+        <v>2024.6708666215684</v>
       </c>
       <c r="S4">
-        <v>340.18163097104696</v>
+        <v>382.84758624176931</v>
       </c>
       <c r="T4">
-        <v>127306.1432527935</v>
+        <v>111392.87534619434</v>
       </c>
       <c r="U4">
         <v>316934.49238931114</v>
       </c>
       <c r="V4">
-        <v>14575.403455900161</v>
+        <v>12753.478023912641</v>
       </c>
       <c r="W4">
-        <v>8165.507408989437</v>
+        <v>8778.9132758991727</v>
       </c>
       <c r="X4">
-        <v>382.19048052714834</v>
+        <v>295.70954009379392</v>
       </c>
       <c r="Y4">
-        <v>91.283555102833432</v>
+        <v>95.147768425281939</v>
       </c>
       <c r="Z4">
-        <v>27802.603065826464</v>
+        <v>24327.277682598167</v>
       </c>
       <c r="AA4">
         <v>69206.876133648</v>
       </c>
       <c r="AB4">
-        <v>552.5655747656931</v>
+        <v>484.28688385028033</v>
       </c>
       <c r="AC4">
-        <v>313.18755906905062</v>
+        <v>336.686670028717</v>
       </c>
       <c r="AD4">
-        <v>1.1539778912488536</v>
+        <v>1.1540064426669374</v>
       </c>
       <c r="AE4">
-        <v>0.25962063569928129</v>
+        <v>0.27911492408533461</v>
       </c>
       <c r="AF4">
-        <v>371.0599104135274</v>
+        <v>285.95409609648021</v>
       </c>
       <c r="AG4">
-        <v>89.864418992600932</v>
+        <v>93.507594951295388</v>
       </c>
       <c r="AH4">
-        <v>27813.733635940083</v>
+        <v>24337.033126595481</v>
       </c>
       <c r="AI4">
-        <v>69208.295269758208</v>
+        <v>69208.516307121958</v>
       </c>
       <c r="AJ4">
-        <v>-1.1299590031018362E-13</v>
+        <v>0</v>
       </c>
       <c r="AK4">
         <v>0</v>
       </c>
       <c r="AL4">
-        <v>28184.793546353609</v>
+        <v>24622.987222691965</v>
       </c>
       <c r="AM4">
-        <v>69298.15968875082</v>
+        <v>69302.023902073284</v>
       </c>
       <c r="AN4">
-        <v>950.10957599272524</v>
+        <v>830.04177351674593</v>
       </c>
       <c r="AO4">
-        <v>1464.576851344719</v>
+        <v>1464.5807754706079</v>
       </c>
       <c r="AP4">
         <v>18.807394940918407</v>
@@ -1958,31 +1958,31 @@
         <v>49</v>
       </c>
       <c r="D5">
-        <v>73.440856797637522</v>
+        <v>73.211623694075882</v>
       </c>
       <c r="E5">
-        <v>71.685181837981077</v>
+        <v>71.737763862111436</v>
       </c>
       <c r="F5">
-        <v>87.860857457809573</v>
+        <v>87.784680847651927</v>
       </c>
       <c r="G5">
-        <v>87.141708748072816</v>
+        <v>87.124354315569136</v>
       </c>
       <c r="H5">
-        <v>222.7421977429814</v>
+        <v>185.61849811915121</v>
       </c>
       <c r="I5">
         <v>221.56851216319822</v>
       </c>
       <c r="J5">
-        <v>893.87953270689</v>
+        <v>744.89961058907511</v>
       </c>
       <c r="K5">
-        <v>529.95510685801241</v>
+        <v>486.23948073440687</v>
       </c>
       <c r="L5">
-        <v>7167.0065959700278</v>
+        <v>5972.505496641691</v>
       </c>
       <c r="M5">
         <v>8708.4676960692723</v>
@@ -1994,82 +1994,82 @@
         <v>39.303724211746172</v>
       </c>
       <c r="P5">
-        <v>4.0130677606868312</v>
+        <v>4.0130677606868321</v>
       </c>
       <c r="Q5">
-        <v>2.3918340276964503</v>
+        <v>2.1945333115576586</v>
       </c>
       <c r="R5">
-        <v>4186.1676192275572</v>
+        <v>3425.4593039065489</v>
       </c>
       <c r="S5">
-        <v>1556.8116502266721</v>
+        <v>1336.4613185213766</v>
       </c>
       <c r="T5">
-        <v>295031.36649092374</v>
+        <v>245859.47207576979</v>
       </c>
       <c r="U5">
-        <v>437895.550011652</v>
+        <v>437895.55001165194</v>
       </c>
       <c r="V5">
-        <v>29899.654748472814</v>
+        <v>24916.378957060682</v>
       </c>
       <c r="W5">
-        <v>21658.738336270639</v>
+        <v>19872.370563217424</v>
       </c>
       <c r="X5">
-        <v>598.96848458372608</v>
+        <v>436.12669170335556</v>
       </c>
       <c r="Y5">
-        <v>289.24699249216968</v>
+        <v>269.39258065522233</v>
       </c>
       <c r="Z5">
-        <v>64424.036280649656</v>
+        <v>53686.696900541348</v>
       </c>
       <c r="AA5">
-        <v>95620.337378444747</v>
+        <v>95620.3373784447</v>
       </c>
       <c r="AB5">
-        <v>1137.9716375556181</v>
+        <v>948.30969796301326</v>
       </c>
       <c r="AC5">
-        <v>829.52897171684606</v>
+        <v>761.34811156963508</v>
       </c>
       <c r="AD5">
-        <v>1.02112476312549</v>
+        <v>1.0199174432371907</v>
       </c>
       <c r="AE5">
-        <v>0.49851220045628508</v>
+        <v>0.45745037985418258</v>
       </c>
       <c r="AF5">
-        <v>578.6854188569157</v>
+        <v>419.24412577602948</v>
       </c>
       <c r="AG5">
-        <v>282.02934484233856</v>
+        <v>263.31383652647094</v>
       </c>
       <c r="AH5">
-        <v>64444.319346376462</v>
+        <v>53703.579466468676</v>
       </c>
       <c r="AI5">
-        <v>95627.555026094589</v>
+        <v>95626.416122573442</v>
       </c>
       <c r="AJ5">
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>9.71716577437275E-14</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>65023.004765233374</v>
+        <v>54122.823592244706</v>
       </c>
       <c r="AM5">
-        <v>95909.584370936922</v>
+        <v>95889.729959099917</v>
       </c>
       <c r="AN5">
-        <v>1655.6141617875069</v>
+        <v>1378.0740145548966</v>
       </c>
       <c r="AO5">
-        <v>2007.1972781970289</v>
+        <v>2007.1795538431666</v>
       </c>
       <c r="AP5">
         <v>24.935723435366441</v>
@@ -2556,121 +2556,121 @@
         <v>122</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>43.690571470396783</v>
+        <v>43.547726728055785</v>
       </c>
       <c r="E3">
-        <v>42.454746312676981</v>
+        <v>42.456728068641723</v>
       </c>
       <c r="F3">
-        <v>81.09635179412308</v>
+        <v>81.006607150104657</v>
       </c>
       <c r="G3">
-        <v>80.776956372261765</v>
+        <v>80.768336799680483</v>
       </c>
       <c r="H3">
-        <v>104.53435477471319</v>
+        <v>91.467560427874034</v>
       </c>
       <c r="I3">
         <v>143.00704677873924</v>
       </c>
       <c r="J3">
-        <v>224.36663340756778</v>
+        <v>196.32080423162179</v>
       </c>
       <c r="K3">
-        <v>200.73241437590545</v>
+        <v>149.67036192155513</v>
       </c>
       <c r="L3">
-        <v>1995.5069727926405</v>
+        <v>1746.0686011935602</v>
       </c>
       <c r="M3">
         <v>5214.1702647945895</v>
       </c>
       <c r="N3">
-        <v>19.08948476405914</v>
+        <v>19.089484764059137</v>
       </c>
       <c r="O3">
         <v>36.460932396303264</v>
       </c>
       <c r="P3">
-        <v>2.1463435048803872</v>
+        <v>2.1463435048803867</v>
       </c>
       <c r="Q3">
-        <v>1.4036540079488462</v>
+        <v>1.0465943133076889</v>
       </c>
       <c r="R3">
-        <v>601.59522627742638</v>
+        <v>511.49201365934181</v>
       </c>
       <c r="S3">
-        <v>360.84641998699266</v>
+        <v>223.27382497456841</v>
       </c>
       <c r="T3">
-        <v>48736.943038917969</v>
+        <v>42644.825159053216</v>
       </c>
       <c r="U3">
         <v>243224.91593453163</v>
       </c>
       <c r="V3">
-        <v>4452.7769850555978</v>
+        <v>3896.1798619236479</v>
       </c>
       <c r="W3">
-        <v>7610.7258758965027</v>
+        <v>5674.7984276026973</v>
       </c>
       <c r="X3">
-        <v>120.02735995121444</v>
+        <v>90.1201306239064</v>
       </c>
       <c r="Y3">
-        <v>79.087562023004324</v>
+        <v>66.629675316765116</v>
       </c>
       <c r="Z3">
-        <v>10643.743085219083</v>
+        <v>9313.2751995666968</v>
       </c>
       <c r="AA3">
         <v>53111.406407041417</v>
       </c>
       <c r="AB3">
-        <v>169.73355505859129</v>
+        <v>148.51686067626869</v>
       </c>
       <c r="AC3">
-        <v>291.83488558988063</v>
+        <v>217.67747985063272</v>
       </c>
       <c r="AD3">
-        <v>0.923784490912283</v>
+        <v>0.92229276830267226</v>
       </c>
       <c r="AE3">
-        <v>0.31528382193045834</v>
+        <v>0.23511685094091103</v>
       </c>
       <c r="AF3">
-        <v>117.29049494700097</v>
+        <v>87.729241455364473</v>
       </c>
       <c r="AG3">
-        <v>77.481654090600728</v>
+        <v>65.736417012307314</v>
       </c>
       <c r="AH3">
-        <v>10646.479950223296</v>
+        <v>9315.6660887352373</v>
       </c>
       <c r="AI3">
-        <v>53113.012314973814</v>
+        <v>53112.299665345869</v>
       </c>
       <c r="AJ3">
-        <v>-4.325851538926287E-14</v>
+        <v>2.1629257694631435E-14</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>-3.5982048360327496E-14</v>
       </c>
       <c r="AL3">
-        <v>10763.770445170296</v>
+        <v>9403.395330190604</v>
       </c>
       <c r="AM3">
-        <v>53190.493969064417</v>
+        <v>53178.036082358187</v>
       </c>
       <c r="AN3">
-        <v>462.40518694834083</v>
+        <v>403.96427978050838</v>
       </c>
       <c r="AO3">
-        <v>1200.866149310031</v>
+        <v>1200.8526725638205</v>
       </c>
       <c r="AP3">
         <v>14.793838572448902</v>
@@ -2696,31 +2696,31 @@
         <v>59</v>
       </c>
       <c r="D4">
-        <v>56.072501839486684</v>
+        <v>55.871402933226911</v>
       </c>
       <c r="E4">
-        <v>54.121387867884273</v>
+        <v>54.149577308386313</v>
       </c>
       <c r="F4">
-        <v>86.576447604888187</v>
+        <v>86.599495819297161</v>
       </c>
       <c r="G4">
-        <v>86.295359119488154</v>
+        <v>86.2973258273861</v>
       </c>
       <c r="H4">
-        <v>168.94859367331856</v>
+        <v>147.83001946415376</v>
       </c>
       <c r="I4">
         <v>163.2443505702883</v>
       </c>
       <c r="J4">
-        <v>577.82181938928818</v>
+        <v>505.56145675216379</v>
       </c>
       <c r="K4">
-        <v>201.57183521836788</v>
+        <v>216.71495084244356</v>
       </c>
       <c r="L4">
-        <v>4100.1198982596379</v>
+        <v>3587.6049109771834</v>
       </c>
       <c r="M4">
         <v>6359.2557610133372</v>
@@ -2732,82 +2732,82 @@
         <v>38.955441574532315</v>
       </c>
       <c r="P4">
-        <v>3.420104345506259</v>
+        <v>3.4198835837585326</v>
       </c>
       <c r="Q4">
-        <v>1.2347859788971802</v>
+        <v>1.3275494685442875</v>
       </c>
       <c r="R4">
-        <v>2358.4013959487852</v>
+        <v>2024.6708666215684</v>
       </c>
       <c r="S4">
-        <v>340.18163097104696</v>
+        <v>382.84758624176931</v>
       </c>
       <c r="T4">
-        <v>127306.1432527935</v>
+        <v>111392.87534619434</v>
       </c>
       <c r="U4">
         <v>316934.49238931114</v>
       </c>
       <c r="V4">
-        <v>14575.403455900161</v>
+        <v>12753.478023912641</v>
       </c>
       <c r="W4">
-        <v>8165.507408989437</v>
+        <v>8778.9132758991727</v>
       </c>
       <c r="X4">
-        <v>382.19048052714834</v>
+        <v>295.70954009379392</v>
       </c>
       <c r="Y4">
-        <v>91.283555102833432</v>
+        <v>95.147768425281939</v>
       </c>
       <c r="Z4">
-        <v>27802.603065826464</v>
+        <v>24327.277682598167</v>
       </c>
       <c r="AA4">
         <v>69206.876133648</v>
       </c>
       <c r="AB4">
-        <v>552.5655747656931</v>
+        <v>484.28688385028033</v>
       </c>
       <c r="AC4">
-        <v>313.18755906905062</v>
+        <v>336.686670028717</v>
       </c>
       <c r="AD4">
-        <v>1.1539778912488536</v>
+        <v>1.1540064426669374</v>
       </c>
       <c r="AE4">
-        <v>0.25962063569928129</v>
+        <v>0.27911492408533461</v>
       </c>
       <c r="AF4">
-        <v>371.0599104135274</v>
+        <v>285.95409609648021</v>
       </c>
       <c r="AG4">
-        <v>89.864418992600932</v>
+        <v>93.507594951295388</v>
       </c>
       <c r="AH4">
-        <v>27813.733635940083</v>
+        <v>24337.033126595481</v>
       </c>
       <c r="AI4">
-        <v>69208.295269758208</v>
+        <v>69208.516307121958</v>
       </c>
       <c r="AJ4">
-        <v>-1.1299590031018362E-13</v>
+        <v>0</v>
       </c>
       <c r="AK4">
         <v>0</v>
       </c>
       <c r="AL4">
-        <v>28184.793546353609</v>
+        <v>24622.987222691965</v>
       </c>
       <c r="AM4">
-        <v>69298.15968875082</v>
+        <v>69302.023902073284</v>
       </c>
       <c r="AN4">
-        <v>950.10957599272524</v>
+        <v>830.04177351674593</v>
       </c>
       <c r="AO4">
-        <v>1464.576851344719</v>
+        <v>1464.5807754706079</v>
       </c>
       <c r="AP4">
         <v>18.807394940918407</v>
@@ -2833,31 +2833,31 @@
         <v>49</v>
       </c>
       <c r="D5">
-        <v>80.142389232237235</v>
+        <v>79.866697557906221</v>
       </c>
       <c r="E5">
-        <v>77.590733883527477</v>
+        <v>77.61419155577741</v>
       </c>
       <c r="F5">
-        <v>97.6816617594317</v>
+        <v>97.658683684433015</v>
       </c>
       <c r="G5">
-        <v>97.384841189738168</v>
+        <v>97.384521306925791</v>
       </c>
       <c r="H5">
-        <v>348.25126511214194</v>
+        <v>304.71985697312419</v>
       </c>
       <c r="I5">
         <v>207.90056424220626</v>
       </c>
       <c r="J5">
-        <v>1550.7244907579791</v>
+        <v>1356.8839294132315</v>
       </c>
       <c r="K5">
-        <v>271.06146357791039</v>
+        <v>250.35922254027673</v>
       </c>
       <c r="L5">
-        <v>12133.992981338595</v>
+        <v>10617.243858671272</v>
       </c>
       <c r="M5">
         <v>9139.7128924086464</v>
@@ -2869,82 +2869,82 @@
         <v>43.961943661493812</v>
       </c>
       <c r="P5">
-        <v>4.4528897555005962</v>
+        <v>4.4528897555005953</v>
       </c>
       <c r="Q5">
-        <v>1.3038034050841778</v>
+        <v>1.2042257963696805</v>
       </c>
       <c r="R5">
-        <v>8387.7617821722033</v>
+        <v>7173.880476222279</v>
       </c>
       <c r="S5">
-        <v>496.45764590886574</v>
+        <v>439.36162323265211</v>
       </c>
       <c r="T5">
-        <v>540910.74023615185</v>
+        <v>473296.89770663285</v>
       </c>
       <c r="U5">
         <v>514049.00353702274</v>
       </c>
       <c r="V5">
-        <v>56168.195708686784</v>
+        <v>49147.171245100915</v>
       </c>
       <c r="W5">
-        <v>12391.703475785702</v>
+        <v>11445.322062842488</v>
       </c>
       <c r="X5">
-        <v>1482.556583672121</v>
+        <v>1131.8259275347098</v>
       </c>
       <c r="Y5">
-        <v>143.04678670888535</v>
+        <v>137.87258909059335</v>
       </c>
       <c r="Z5">
-        <v>118130.40769733707</v>
+        <v>103364.10673516999</v>
       </c>
       <c r="AA5">
         <v>112249.46027872519</v>
       </c>
       <c r="AB5">
-        <v>2136.862668768028</v>
+        <v>1869.7548351720091</v>
       </c>
       <c r="AC5">
-        <v>475.31468517154906</v>
+        <v>439.04402639145252</v>
       </c>
       <c r="AD5">
-        <v>1.0491275514366969</v>
+        <v>1.0474315843388802</v>
       </c>
       <c r="AE5">
-        <v>0.24291984584026707</v>
+        <v>0.22437337557496775</v>
       </c>
       <c r="AF5">
-        <v>1443.4246946843782</v>
+        <v>1097.6408883363754</v>
       </c>
       <c r="AG5">
-        <v>141.03155866119</v>
+        <v>136.15326011675421</v>
       </c>
       <c r="AH5">
-        <v>118169.53958632483</v>
+        <v>103398.29177436832</v>
       </c>
       <c r="AI5">
-        <v>112251.4755067729</v>
+        <v>112251.17960769903</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>4.80107986297752E-13</v>
       </c>
       <c r="AK5">
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>119612.96428100919</v>
+        <v>104495.93266270471</v>
       </c>
       <c r="AM5">
-        <v>112392.50706543408</v>
+        <v>112387.33286781579</v>
       </c>
       <c r="AN5">
-        <v>2811.7800260485265</v>
+        <v>2456.4191518072284</v>
       </c>
       <c r="AO5">
-        <v>2104.9291922118787</v>
+        <v>2104.9244835726263</v>
       </c>
       <c r="AP5">
         <v>27.002110200544795</v>
